--- a/Digitised_Records_Form.xlsx
+++ b/Digitised_Records_Form.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sotonac-my.sharepoint.com/personal/ck1g20_soton_ac_uk/Documents/Documents/PhD/20_Historical_record_catalogue/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="8_{CE1C8314-5B9F-418D-ABC5-C0F131808328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6C7EE93-6FA9-4D5F-8618-12A479E4E903}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="8_{CE1C8314-5B9F-418D-ABC5-C0F131808328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57CF2B68-CBA3-459B-AE42-B7109924C1BC}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8B47D44B-FC3B-4D4A-ACC6-526F2F8A5E24}"/>
   </bookViews>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
-  <si>
-    <t>Study</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Location</t>
   </si>
@@ -145,12 +142,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -507,23 +503,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
+      <c r="A1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1"/>
+      <c r="C1"/>
+      <c r="D1"/>
+      <c r="E1"/>
+      <c r="F1"/>
+      <c r="G1"/>
+      <c r="H1"/>
+      <c r="I1"/>
+      <c r="J1"/>
+      <c r="K1"/>
+      <c r="L1"/>
+      <c r="M1"/>
+      <c r="N1"/>
+      <c r="O1"/>
       <c r="P1"/>
       <c r="Q1"/>
       <c r="R1"/>
@@ -533,51 +529,47 @@
       <c r="V1"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O3" s="1" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -593,7 +585,6 @@
       <c r="O4" s="3"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -609,7 +600,6 @@
       <c r="O5" s="3"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -625,7 +615,6 @@
       <c r="O6" s="3"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -641,7 +630,6 @@
       <c r="O7" s="3"/>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -657,7 +645,6 @@
       <c r="O8" s="3"/>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
